--- a/Hoadon/HD2026/HDVao/4/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDVao/4/3502550210_HDDienTuMayTinhTien.xlsx
@@ -211,7 +211,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Từ ngày 01/04/2026 đến ngày 24/04/2026</t>
+          <t>Từ ngày 01/04/2026 đến ngày 30/04/2026</t>
         </is>
       </c>
     </row>
@@ -318,12 +318,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>82246</t>
+          <t>103597</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -353,16 +353,16 @@
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="13" t="n">
-        <v>5016000.0</v>
+        <v>2722200.0</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>501600.0</v>
+        <v>217776.0</v>
       </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>5517600.0</v>
+        <v>2939976.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -391,12 +391,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>89980</t>
+          <t>82246</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -426,20 +426,20 @@
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="13" t="n">
-        <v>1.937378E7</v>
+        <v>5016000.0</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>1886267.0</v>
+        <v>501600.0</v>
       </c>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>2.1260047E7</v>
+        <v>5517600.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn đã bị điều chỉnh</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
@@ -464,7 +464,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>90001</t>
+          <t>89980</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -499,20 +499,20 @@
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="13" t="n">
-        <v>1.7573784E7</v>
+        <v>1.937378E7</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>1706267.0</v>
+        <v>1886267.0</v>
       </c>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>1.9280051E7</v>
+        <v>2.1260047E7</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị điều chỉnh</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>90114</t>
+          <t>90001</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -572,20 +572,20 @@
       </c>
       <c r="K10" s="6"/>
       <c r="L10" s="13" t="n">
-        <v>-1.937378E7</v>
+        <v>1.7573784E7</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>-1886267.0</v>
+        <v>1706267.0</v>
       </c>
       <c r="N10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>-2.1260047E7</v>
+        <v>1.9280051E7</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn điều chỉnh</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>90877</t>
+          <t>90114</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -645,20 +645,20 @@
       </c>
       <c r="K11" s="6"/>
       <c r="L11" s="13" t="n">
-        <v>1799996.0</v>
+        <v>-1.937378E7</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>180000.0</v>
+        <v>-1886267.0</v>
       </c>
       <c r="N11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1979996.0</v>
+        <v>-2.1260047E7</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn điều chỉnh</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>98088</t>
+          <t>90877</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -718,20 +718,20 @@
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="13" t="n">
-        <v>1.3287677E7</v>
+        <v>1799996.0</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>1148468.0</v>
+        <v>180000.0</v>
       </c>
       <c r="N12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1.4436145E7</v>
+        <v>1979996.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn đã bị điều chỉnh</t>
+          <t>Hóa đơn mới</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>98135</t>
+          <t>98088</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -791,20 +791,20 @@
       </c>
       <c r="K13" s="6"/>
       <c r="L13" s="13" t="n">
-        <v>-1.3287677E7</v>
+        <v>1.3287677E7</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>-1148468.0</v>
+        <v>1148468.0</v>
       </c>
       <c r="N13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>-1.4436145E7</v>
+        <v>1.4436145E7</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn điều chỉnh</t>
+          <t>Hóa đơn đã bị điều chỉnh</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C26MTQ</t>
+          <t>C26MVT</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>98135</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -839,17 +839,17 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>0302478297</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TRẦN QUANG VIỆT NAM</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>621 Xô Viết Nghệ Tĩnh, Phường Bình Thạnh, Thành Phố Hồ Chí Minh</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -859,25 +859,25 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CONG TY TNHH THANH HUONG BEN DINH</t>
         </is>
       </c>
       <c r="K14" s="6"/>
       <c r="L14" s="13" t="n">
-        <v>7.8055555E7</v>
+        <v>-1.3287677E7</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>6244445.0</v>
+        <v>-1148468.0</v>
       </c>
       <c r="N14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>8.43E7</v>
+        <v>-1.4436145E7</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn điều chỉnh</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
@@ -892,37 +892,37 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C26MTS</t>
+          <t>C26MVT</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>98893</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>042182000628</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ SONG</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>1/16/15B Ngô Đức Kế, Phường Tam Thắng, TP - HCM</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -932,21 +932,25 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CONG TY TNHH THANH HUONG BEN DINH</t>
         </is>
       </c>
       <c r="K15" s="6"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
+      <c r="L15" s="13" t="n">
+        <v>1.188568E7</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>1036309.0</v>
+      </c>
       <c r="N15" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>1869000.0</v>
+        <v>1.2921989E7</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn đã bị thay thế</t>
+          <t>Hóa đơn đã bị điều chỉnh</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
@@ -961,37 +965,37 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C26MTS</t>
+          <t>C26MVT</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>99091</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>042182000628</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ SONG</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>1/16/15B Ngô Đức Kế, Phường Tam Thắng, TP - HCM</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
@@ -1001,21 +1005,25 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CONG TY TNHH THANH HUONG BEN DINH</t>
         </is>
       </c>
       <c r="K16" s="6"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
+      <c r="L16" s="13" t="n">
+        <v>-1.188568E7</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>-1036309.0</v>
+      </c>
       <c r="N16" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>1869000.0</v>
+        <v>-1.2921989E7</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn thay thế</t>
+          <t>Hóa đơn điều chỉnh</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
@@ -1030,37 +1038,37 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C26MTT</t>
+          <t>C26MVT</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>99792</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>051076001913</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CÀ PHÊ THÁI NGUYÊN</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Tổ 15 khu phố Hải Dinh, Phường Long Hương, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
@@ -1070,17 +1078,21 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>CONG TY TNHH THANH HUONG BEN DINH</t>
         </is>
       </c>
       <c r="K17" s="6"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
+      <c r="L17" s="13" t="n">
+        <v>1.219448E7</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>1083522.0</v>
+      </c>
       <c r="N17" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>4300000.0</v>
+        <v>1.3278002E7</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1099,37 +1111,37 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>C26MTT</t>
+          <t>C26MTQ</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>051076001913</t>
+          <t>0302478297</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CÀ PHÊ THÁI NGUYÊN</t>
+          <t>CÔNG TY TNHH TRẦN QUANG VIỆT NAM</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Tổ 15 khu phố Hải Dinh, Phường Long Hương, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>621 Xô Viết Nghệ Tĩnh, Phường Bình Thạnh, Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -1143,13 +1155,17 @@
         </is>
       </c>
       <c r="K18" s="6"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
+      <c r="L18" s="13" t="n">
+        <v>7.8055555E7</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>6244445.0</v>
+      </c>
       <c r="N18" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>3850000.0</v>
+        <v>8.43E7</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -1173,32 +1189,32 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>C26MTT</t>
+          <t>C26MTS</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>077082002684</t>
+          <t>042182000628</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG HOÀI MINH ANH</t>
+          <t>HỘ KINH DOANH NGUYỄN THỊ SONG</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Số 41Y, khu phố Long Phượng, Xã Long Điền, TP Hồ Chí Minh</t>
+          <t>1/16/15B Ngô Đức Kế, Phường Tam Thắng, TP - HCM</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -1218,11 +1234,11 @@
         <v>0.0</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>2344000.0</v>
+        <v>1869000.0</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị thay thế</t>
         </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
@@ -1242,32 +1258,32 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>C26MHH</t>
+          <t>C26MTS</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>077195006087</t>
+          <t>042182000628</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH TẠP HOÁ HỒNG HẠNH</t>
+          <t>HỘ KINH DOANH NGUYỄN THỊ SONG</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Khu TĐC khu phố Tây Hoà Long, Phường Tam Long, TP Hồ Chí Minh</t>
+          <t>1/16/15B Ngô Đức Kế, Phường Tam Thắng, TP - HCM</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -1287,11 +1303,11 @@
         <v>0.0</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>2900000.0</v>
+        <v>1869000.0</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn thay thế</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
@@ -1311,32 +1327,32 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>C26MHH</t>
+          <t>C26MTT</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>077195006087</t>
+          <t>051076001913</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH TẠP HOÁ HỒNG HẠNH</t>
+          <t>HỘ KINH DOANH CÀ PHÊ THÁI NGUYÊN</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Khu TĐC khu phố Tây Hoà Long, Phường Tam Long, TP Hồ Chí Minh</t>
+          <t>Tổ 15 khu phố Hải Dinh, Phường Long Hương, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -1356,7 +1372,7 @@
         <v>0.0</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>837000.0</v>
+        <v>4300000.0</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
@@ -1380,32 +1396,32 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>C26MHH</t>
+          <t>C26MTT</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>93</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>077195006087</t>
+          <t>051076001913</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH TẠP HOÁ HỒNG HẠNH</t>
+          <t>HỘ KINH DOANH CÀ PHÊ THÁI NGUYÊN</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Khu TĐC khu phố Tây Hoà Long, Phường Tam Long, TP Hồ Chí Minh</t>
+          <t>Tổ 15 khu phố Hải Dinh, Phường Long Hương, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
@@ -1425,7 +1441,7 @@
         <v>0.0</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>2300000.0</v>
+        <v>3850000.0</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
@@ -1449,32 +1465,32 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>C26MHH</t>
+          <t>C26MTT</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>077195006087</t>
+          <t>066090005963</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH TẠP HOÁ HỒNG HẠNH</t>
+          <t>HỘ KINH DOANH CÚC LÂM</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Khu TĐC khu phố Tây Hoà Long, Phường Tam Long, TP Hồ Chí Minh</t>
+          <t>888/3/4 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -1494,7 +1510,7 @@
         <v>0.0</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>1500000.0</v>
+        <v>9792000.0</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
@@ -1518,32 +1534,32 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MTT</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>077196000132</t>
+          <t>066090005963</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Hộ kinh doanh Nguyễn Thị Minh Tuyền (NCC hiền trang)</t>
+          <t>HỘ KINH DOANH CÚC LÂM</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>441/6/4 đường Trần Phú, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>888/3/4 đường 30/4, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
@@ -1563,7 +1579,7 @@
         <v>0.0</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>4680000.0</v>
+        <v>1422900.0</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
@@ -1587,32 +1603,32 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MTT</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>57</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>077196000132</t>
+          <t>077082002684</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Hộ kinh doanh Nguyễn Thị Minh Tuyền (NCC hiền trang)</t>
+          <t>HỘ KINH DOANH CỬA HÀNG HOÀI MINH ANH</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>441/6/4 đường Trần Phú, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 41Y, khu phố Long Phượng, Xã Long Điền, TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
@@ -1632,7 +1648,7 @@
         <v>0.0</v>
       </c>
       <c r="O25" s="13" t="n">
-        <v>3050000.0</v>
+        <v>2344000.0</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
@@ -1656,32 +1672,32 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>C26MMM</t>
+          <t>C26MTT</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>079056002409</t>
+          <t>077082002684</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Cường Hưng</t>
+          <t>HỘ KINH DOANH CỬA HÀNG HOÀI MINH ANH</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>390i, Nguyễn Duy, Phường Chánh Hưng, Hồ Chí Minh, Việt Nam</t>
+          <t>Số 41Y, khu phố Long Phượng, Xã Long Điền, TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -1701,7 +1717,7 @@
         <v>0.0</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>3400000.0</v>
+        <v>2566500.0</v>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
@@ -1725,32 +1741,32 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>C26MMM</t>
+          <t>C26MHH</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>47</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>079056002409</t>
+          <t>077195006087</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Cường Hưng</t>
+          <t>HỘ KINH DOANH TẠP HOÁ HỒNG HẠNH</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>390i, Nguyễn Duy, Phường Chánh Hưng, Hồ Chí Minh, Việt Nam</t>
+          <t>Khu TĐC khu phố Tây Hoà Long, Phường Tam Long, TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -1770,7 +1786,7 @@
         <v>0.0</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>3400000.0</v>
+        <v>2900000.0</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
@@ -1789,7 +1805,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1799,27 +1815,27 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>3500354108</t>
+          <t>077195006087</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN XĂNG DẦU LONG PHƯỚC</t>
+          <t>HỘ KINH DOANH TẠP HOÁ HỒNG HẠNH</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Số 3 Trần Phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Khu TĐC khu phố Tây Hoà Long, Phường Tam Long, TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -1833,15 +1849,13 @@
         </is>
       </c>
       <c r="K28" s="6"/>
-      <c r="L28" s="13" t="n">
-        <v>2321222.0</v>
-      </c>
-      <c r="M28" s="13" t="n">
-        <v>185698.0</v>
-      </c>
-      <c r="N28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O28" s="13" t="n">
-        <v>2506920.0</v>
+        <v>837000.0</v>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
@@ -1860,7 +1874,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1870,7 +1884,7 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>12501</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -1880,17 +1894,17 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>3500354108</t>
+          <t>077195006087</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN XĂNG DẦU LONG PHƯỚC</t>
+          <t>HỘ KINH DOANH TẠP HOÁ HỒNG HẠNH</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Số 3 Trần Phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Khu TĐC khu phố Tây Hoà Long, Phường Tam Long, TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
@@ -1904,15 +1918,13 @@
         </is>
       </c>
       <c r="K29" s="6"/>
-      <c r="L29" s="13" t="n">
-        <v>710000.0</v>
-      </c>
-      <c r="M29" s="13" t="n">
-        <v>71000.0</v>
-      </c>
-      <c r="N29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O29" s="13" t="n">
-        <v>781000.0</v>
+        <v>2300000.0</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
@@ -1931,37 +1943,37 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>C26MRV</t>
+          <t>C26MHH</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>16814</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>077195006087</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>HỘ KINH DOANH TẠP HOÁ HỒNG HẠNH</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Khu TĐC khu phố Tây Hoà Long, Phường Tam Long, TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -1975,17 +1987,13 @@
         </is>
       </c>
       <c r="K30" s="6"/>
-      <c r="L30" s="13" t="n">
-        <v>4726000.0</v>
-      </c>
-      <c r="M30" s="13" t="n">
-        <v>378080.0</v>
-      </c>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
       <c r="N30" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>5104080.0</v>
+        <v>1500000.0</v>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
@@ -2004,37 +2012,37 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>C26MRV</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>54</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>077196000132</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Hộ kinh doanh Nguyễn Thị Minh Tuyền (NCC hiền trang)</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>441/6/4 đường Trần Phú, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
@@ -2048,17 +2056,13 @@
         </is>
       </c>
       <c r="K31" s="6"/>
-      <c r="L31" s="13" t="n">
-        <v>2934800.0</v>
-      </c>
-      <c r="M31" s="13" t="n">
-        <v>234784.0</v>
-      </c>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
       <c r="N31" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>3169584.0</v>
+        <v>4680000.0</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
@@ -2077,37 +2081,37 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>C26MRV</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>17263</t>
+          <t>59</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>077196000132</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Hộ kinh doanh Nguyễn Thị Minh Tuyền (NCC hiền trang)</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>441/6/4 đường Trần Phú, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
@@ -2121,17 +2125,13 @@
         </is>
       </c>
       <c r="K32" s="6"/>
-      <c r="L32" s="13" t="n">
-        <v>1553000.0</v>
-      </c>
-      <c r="M32" s="13" t="n">
-        <v>124240.0</v>
-      </c>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
       <c r="N32" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>1677240.0</v>
+        <v>3050000.0</v>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
@@ -2150,37 +2150,37 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>C26MRV</t>
+          <t>C26MMM</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>079056002409</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Cường Hưng</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>390i, Nguyễn Duy, Phường Chánh Hưng, Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -2194,17 +2194,13 @@
         </is>
       </c>
       <c r="K33" s="6"/>
-      <c r="L33" s="13" t="n">
-        <v>4654300.0</v>
-      </c>
-      <c r="M33" s="13" t="n">
-        <v>372344.0</v>
-      </c>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
       <c r="N33" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>5026644.0</v>
+        <v>3400000.0</v>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
@@ -2223,37 +2219,37 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>C26MRV</t>
+          <t>C26MMM</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>17690</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>079056002409</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Cường Hưng</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>390i, Nguyễn Duy, Phường Chánh Hưng, Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
@@ -2267,17 +2263,13 @@
         </is>
       </c>
       <c r="K34" s="6"/>
-      <c r="L34" s="13" t="n">
-        <v>1267723.0</v>
-      </c>
-      <c r="M34" s="13" t="n">
-        <v>101418.0</v>
-      </c>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
       <c r="N34" s="13" t="n">
-        <v>13377.0</v>
+        <v>0.0</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>1369141.0</v>
+        <v>3400000.0</v>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
@@ -2301,32 +2293,32 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>C26MRV</t>
+          <t>C26MHH</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>17972</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>3500354108</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>DOANH NGHIỆP TƯ NHÂN XĂNG DẦU LONG PHƯỚC</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 3 Trần Phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
@@ -2341,16 +2333,14 @@
       </c>
       <c r="K35" s="6"/>
       <c r="L35" s="13" t="n">
-        <v>8472222.0</v>
+        <v>2321222.0</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>677778.0</v>
-      </c>
-      <c r="N35" s="13" t="n">
-        <v>383778.0</v>
-      </c>
+        <v>185698.0</v>
+      </c>
+      <c r="N35" s="13"/>
       <c r="O35" s="13" t="n">
-        <v>9150000.0</v>
+        <v>2506920.0</v>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
@@ -2374,32 +2364,32 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>C26MRV</t>
+          <t>C26MHH</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>18008</t>
+          <t>12501</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>3500354108</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>DOANH NGHIỆP TƯ NHÂN XĂNG DẦU LONG PHƯỚC</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 3 Trần Phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
@@ -2414,16 +2404,14 @@
       </c>
       <c r="K36" s="6"/>
       <c r="L36" s="13" t="n">
-        <v>1146540.0</v>
+        <v>710000.0</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>91723.0</v>
-      </c>
-      <c r="N36" s="13" t="n">
-        <v>35460.0</v>
-      </c>
+        <v>71000.0</v>
+      </c>
+      <c r="N36" s="13"/>
       <c r="O36" s="13" t="n">
-        <v>1238263.0</v>
+        <v>781000.0</v>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
@@ -2452,12 +2440,12 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>18344</t>
+          <t>16814</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -2487,16 +2475,16 @@
       </c>
       <c r="K37" s="6"/>
       <c r="L37" s="13" t="n">
-        <v>1212400.0</v>
+        <v>4726000.0</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>96992.0</v>
+        <v>378080.0</v>
       </c>
       <c r="N37" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>1309392.0</v>
+        <v>5104080.0</v>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
@@ -2525,12 +2513,12 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>18594</t>
+          <t>17018</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -2560,16 +2548,16 @@
       </c>
       <c r="K38" s="6"/>
       <c r="L38" s="13" t="n">
-        <v>1884000.0</v>
+        <v>2934800.0</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>150720.0</v>
+        <v>234784.0</v>
       </c>
       <c r="N38" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>2034720.0</v>
+        <v>3169584.0</v>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
@@ -2598,12 +2586,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>18820</t>
+          <t>17263</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -2633,16 +2621,16 @@
       </c>
       <c r="K39" s="6"/>
       <c r="L39" s="13" t="n">
-        <v>2820850.0</v>
+        <v>1553000.0</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>225668.0</v>
+        <v>124240.0</v>
       </c>
       <c r="N39" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>3046518.0</v>
+        <v>1677240.0</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
@@ -2671,12 +2659,12 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>19058</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -2706,16 +2694,16 @@
       </c>
       <c r="K40" s="6"/>
       <c r="L40" s="13" t="n">
-        <v>4048700.0</v>
+        <v>4654300.0</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>323896.0</v>
+        <v>372344.0</v>
       </c>
       <c r="N40" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O40" s="13" t="n">
-        <v>4372596.0</v>
+        <v>5026644.0</v>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
@@ -2744,12 +2732,12 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>19059</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -2779,16 +2767,16 @@
       </c>
       <c r="K41" s="6"/>
       <c r="L41" s="13" t="n">
-        <v>1488400.0</v>
+        <v>1267723.0</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>119072.0</v>
+        <v>101418.0</v>
       </c>
       <c r="N41" s="13" t="n">
-        <v>0.0</v>
+        <v>13377.0</v>
       </c>
       <c r="O41" s="13" t="n">
-        <v>1607472.0</v>
+        <v>1369141.0</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
@@ -2817,12 +2805,12 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>17972</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -2852,16 +2840,16 @@
       </c>
       <c r="K42" s="6"/>
       <c r="L42" s="13" t="n">
-        <v>1057050.0</v>
+        <v>8472222.0</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>84564.0</v>
+        <v>677778.0</v>
       </c>
       <c r="N42" s="13" t="n">
-        <v>0.0</v>
+        <v>383778.0</v>
       </c>
       <c r="O42" s="13" t="n">
-        <v>1141614.0</v>
+        <v>9150000.0</v>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
@@ -2890,12 +2878,12 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>19746</t>
+          <t>18008</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -2925,16 +2913,16 @@
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="13" t="n">
-        <v>4541700.0</v>
+        <v>1146540.0</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>363336.0</v>
+        <v>91723.0</v>
       </c>
       <c r="N43" s="13" t="n">
-        <v>0.0</v>
+        <v>35460.0</v>
       </c>
       <c r="O43" s="13" t="n">
-        <v>4905036.0</v>
+        <v>1238263.0</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
@@ -2963,12 +2951,12 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>19853</t>
+          <t>18344</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -2998,16 +2986,16 @@
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="13" t="n">
-        <v>1334400.0</v>
+        <v>1212400.0</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>106752.0</v>
+        <v>96992.0</v>
       </c>
       <c r="N44" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O44" s="13" t="n">
-        <v>1441152.0</v>
+        <v>1309392.0</v>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
@@ -3036,12 +3024,12 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>20453</t>
+          <t>18594</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -3071,16 +3059,16 @@
       </c>
       <c r="K45" s="6"/>
       <c r="L45" s="13" t="n">
-        <v>3192515.0</v>
+        <v>1884000.0</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>255401.0</v>
+        <v>150720.0</v>
       </c>
       <c r="N45" s="13" t="n">
-        <v>56485.0</v>
+        <v>0.0</v>
       </c>
       <c r="O45" s="13" t="n">
-        <v>3447916.0</v>
+        <v>2034720.0</v>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
@@ -3109,12 +3097,12 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>20454</t>
+          <t>18820</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -3144,16 +3132,16 @@
       </c>
       <c r="K46" s="6"/>
       <c r="L46" s="13" t="n">
-        <v>5967300.0</v>
+        <v>2820850.0</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>477384.0</v>
+        <v>225668.0</v>
       </c>
       <c r="N46" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O46" s="13" t="n">
-        <v>6444684.0</v>
+        <v>3046518.0</v>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
@@ -3182,12 +3170,12 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>20505</t>
+          <t>19058</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -3217,16 +3205,16 @@
       </c>
       <c r="K47" s="6"/>
       <c r="L47" s="13" t="n">
-        <v>2106700.0</v>
+        <v>4048700.0</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>168536.0</v>
+        <v>323896.0</v>
       </c>
       <c r="N47" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O47" s="13" t="n">
-        <v>2275236.0</v>
+        <v>4372596.0</v>
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
@@ -3255,12 +3243,12 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>20506</t>
+          <t>19059</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -3290,16 +3278,16 @@
       </c>
       <c r="K48" s="6"/>
       <c r="L48" s="13" t="n">
-        <v>0.0</v>
+        <v>1488400.0</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>0.0</v>
+        <v>119072.0</v>
       </c>
       <c r="N48" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O48" s="13" t="n">
-        <v>0.0</v>
+        <v>1607472.0</v>
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
@@ -3328,12 +3316,12 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>20925</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -3363,16 +3351,16 @@
       </c>
       <c r="K49" s="6"/>
       <c r="L49" s="13" t="n">
-        <v>288090.0</v>
+        <v>1057050.0</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>23047.0</v>
+        <v>84564.0</v>
       </c>
       <c r="N49" s="13" t="n">
-        <v>8910.0</v>
+        <v>0.0</v>
       </c>
       <c r="O49" s="13" t="n">
-        <v>311137.0</v>
+        <v>1141614.0</v>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
@@ -3396,12 +3384,12 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>C26MRT</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>10173</t>
+          <t>19746</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
@@ -3411,17 +3399,17 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>3501013206</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -3436,16 +3424,16 @@
       </c>
       <c r="K50" s="6"/>
       <c r="L50" s="13" t="n">
-        <v>1.3888889E7</v>
+        <v>4541700.0</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>1111111.0</v>
+        <v>363336.0</v>
       </c>
       <c r="N50" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O50" s="13" t="n">
-        <v>1.5E7</v>
+        <v>4905036.0</v>
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
@@ -3469,32 +3457,32 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>C26MTP</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>19853</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>3501981599</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI THỊNH PHÁT VN</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Số 138 Nguyễn Thiện Thuật, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -3504,21 +3492,21 @@
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>Công ty TNHH Thạnh Hương Bến Đình</t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K51" s="6"/>
       <c r="L51" s="13" t="n">
-        <v>5.3909091E7</v>
+        <v>1334400.0</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>5390909.0</v>
+        <v>106752.0</v>
       </c>
       <c r="N51" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O51" s="13" t="n">
-        <v>5.93E7</v>
+        <v>1441152.0</v>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
@@ -3542,32 +3530,32 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>20453</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -3582,16 +3570,16 @@
       </c>
       <c r="K52" s="6"/>
       <c r="L52" s="13" t="n">
-        <v>2.9281817E7</v>
+        <v>3192515.0</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>2928183.0</v>
+        <v>255401.0</v>
       </c>
       <c r="N52" s="13" t="n">
-        <v>0.0</v>
+        <v>56485.0</v>
       </c>
       <c r="O52" s="13" t="n">
-        <v>3.221E7</v>
+        <v>3447916.0</v>
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
@@ -3615,32 +3603,32 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>20454</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -3655,16 +3643,16 @@
       </c>
       <c r="K53" s="6"/>
       <c r="L53" s="13" t="n">
-        <v>5051851.0</v>
+        <v>5967300.0</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>428149.0</v>
+        <v>477384.0</v>
       </c>
       <c r="N53" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O53" s="13" t="n">
-        <v>5480000.0</v>
+        <v>6444684.0</v>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
@@ -3688,32 +3676,32 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>20505</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -3728,16 +3716,16 @@
       </c>
       <c r="K54" s="6"/>
       <c r="L54" s="13" t="n">
-        <v>7772727.0</v>
+        <v>2106700.0</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>777273.0</v>
+        <v>168536.0</v>
       </c>
       <c r="N54" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O54" s="13" t="n">
-        <v>8550000.0</v>
+        <v>2275236.0</v>
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
@@ -3761,32 +3749,32 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>20506</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
@@ -3801,16 +3789,16 @@
       </c>
       <c r="K55" s="6"/>
       <c r="L55" s="13" t="n">
-        <v>4.0636363E7</v>
+        <v>0.0</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>4063637.0</v>
+        <v>0.0</v>
       </c>
       <c r="N55" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O55" s="13" t="n">
-        <v>4.47E7</v>
+        <v>0.0</v>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
@@ -3834,32 +3822,32 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>20925</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
@@ -3874,16 +3862,16 @@
       </c>
       <c r="K56" s="6"/>
       <c r="L56" s="13" t="n">
-        <v>2.4204545E7</v>
+        <v>288090.0</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>2420455.0</v>
+        <v>23047.0</v>
       </c>
       <c r="N56" s="13" t="n">
-        <v>0.0</v>
+        <v>8910.0</v>
       </c>
       <c r="O56" s="13" t="n">
-        <v>2.6625E7</v>
+        <v>311137.0</v>
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
@@ -3907,32 +3895,32 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>21207</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
@@ -3947,16 +3935,16 @@
       </c>
       <c r="K57" s="6"/>
       <c r="L57" s="13" t="n">
-        <v>2.4444444E7</v>
+        <v>5740750.0</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>1955556.0</v>
+        <v>459260.0</v>
       </c>
       <c r="N57" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O57" s="13" t="n">
-        <v>2.64E7</v>
+        <v>6200010.0</v>
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
@@ -3980,32 +3968,32 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>21494</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
@@ -4020,16 +4008,16 @@
       </c>
       <c r="K58" s="6"/>
       <c r="L58" s="13" t="n">
-        <v>1.3609091E7</v>
+        <v>1123200.0</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>1360909.0</v>
+        <v>89856.0</v>
       </c>
       <c r="N58" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O58" s="13" t="n">
-        <v>1.497E7</v>
+        <v>1213056.0</v>
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
@@ -4053,32 +4041,32 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>C26MDH</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>22090</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>3502399055</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
@@ -4093,16 +4081,16 @@
       </c>
       <c r="K59" s="6"/>
       <c r="L59" s="13" t="n">
-        <v>1741667.0</v>
+        <v>4155300.0</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>139333.0</v>
+        <v>332424.0</v>
       </c>
       <c r="N59" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>1881000.0</v>
+        <v>4487724.0</v>
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
@@ -4126,32 +4114,32 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>C26MDH</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>22171</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>3502399055</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
@@ -4166,16 +4154,16 @@
       </c>
       <c r="K60" s="6"/>
       <c r="L60" s="13" t="n">
-        <v>1429630.0</v>
+        <v>1870370.0</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>114370.0</v>
+        <v>149630.0</v>
       </c>
       <c r="N60" s="13" t="n">
-        <v>0.0</v>
+        <v>250630.0</v>
       </c>
       <c r="O60" s="13" t="n">
-        <v>1544000.0</v>
+        <v>2020000.0</v>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
@@ -4199,32 +4187,32 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>22404</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>3502478885</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ LINH CHÂU VŨNG TÀU</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Số 43 Đường Nguyễn Quyền, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
@@ -4239,16 +4227,16 @@
       </c>
       <c r="K61" s="6"/>
       <c r="L61" s="13" t="n">
-        <v>2036944.0</v>
+        <v>2481358.0</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>162956.0</v>
+        <v>198509.0</v>
       </c>
       <c r="N61" s="13" t="n">
-        <v>0.0</v>
+        <v>164842.0</v>
       </c>
       <c r="O61" s="13" t="n">
-        <v>2199900.0</v>
+        <v>2679867.0</v>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
@@ -4272,12 +4260,12 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MRT</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
@@ -4287,17 +4275,17 @@
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>3502483525</t>
+          <t>3501013206</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
@@ -4307,21 +4295,21 @@
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K62" s="6"/>
       <c r="L62" s="13" t="n">
-        <v>2.5816345E7</v>
+        <v>1.3888889E7</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>2581635.0</v>
+        <v>1111111.0</v>
       </c>
       <c r="N62" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>2.839798E7</v>
+        <v>1.5E7</v>
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
@@ -4345,32 +4333,32 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>C26MUN</t>
+          <t>C26MTP</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>3502545972</t>
+          <t>3501981599</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH UYÊN NGUYỄN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI THỊNH PHÁT VN</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Số 03 đường Nguyễn Gia Thiều, Phường Phước Thắng, TP Hồ Chí Minh</t>
+          <t>Số 138 Nguyễn Thiện Thuật, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
@@ -4380,21 +4368,21 @@
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t>Công ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
       <c r="K63" s="6"/>
       <c r="L63" s="13" t="n">
-        <v>1.054546E8</v>
+        <v>5.3909091E7</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>1.054546E7</v>
+        <v>5390909.0</v>
       </c>
       <c r="N63" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>1.1600006E8</v>
+        <v>5.93E7</v>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
@@ -4418,32 +4406,32 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MHT</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502324074</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HƯƠNG THỊNH PHÁT</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>69 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -4458,16 +4446,16 @@
       </c>
       <c r="K64" s="6"/>
       <c r="L64" s="13" t="n">
-        <v>1407408.0</v>
+        <v>4.8346603E8</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>112592.0</v>
+        <v>4.8346603E7</v>
       </c>
       <c r="N64" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O64" s="13" t="n">
-        <v>1520000.0</v>
+        <v>5.31812633E8</v>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
@@ -4491,32 +4479,32 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -4531,16 +4519,16 @@
       </c>
       <c r="K65" s="6"/>
       <c r="L65" s="13" t="n">
-        <v>2.5555556E7</v>
+        <v>2.9281817E7</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>2044444.0</v>
+        <v>2928183.0</v>
       </c>
       <c r="N65" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O65" s="13" t="n">
-        <v>2.76E7</v>
+        <v>3.221E7</v>
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
@@ -4564,12 +4552,12 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
@@ -4579,17 +4567,17 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
@@ -4604,16 +4592,16 @@
       </c>
       <c r="K66" s="6"/>
       <c r="L66" s="13" t="n">
-        <v>2592593.0</v>
+        <v>5051851.0</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>207407.0</v>
+        <v>428149.0</v>
       </c>
       <c r="N66" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O66" s="13" t="n">
-        <v>2800000.0</v>
+        <v>5480000.0</v>
       </c>
       <c r="P66" s="6" t="inlineStr">
         <is>
@@ -4637,12 +4625,12 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
@@ -4652,17 +4640,17 @@
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
@@ -4677,16 +4665,16 @@
       </c>
       <c r="K67" s="6"/>
       <c r="L67" s="13" t="n">
-        <v>4150000.0</v>
+        <v>7772727.0</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>332000.0</v>
+        <v>777273.0</v>
       </c>
       <c r="N67" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O67" s="13" t="n">
-        <v>4482000.0</v>
+        <v>8550000.0</v>
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
@@ -4710,32 +4698,32 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
@@ -4750,23 +4738,1556 @@
       </c>
       <c r="K68" s="6"/>
       <c r="L68" s="13" t="n">
+        <v>4.0636363E7</v>
+      </c>
+      <c r="M68" s="13" t="n">
+        <v>4063637.0</v>
+      </c>
+      <c r="N68" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O68" s="13" t="n">
+        <v>4.47E7</v>
+      </c>
+      <c r="P68" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>63.0</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K69" s="6"/>
+      <c r="L69" s="13" t="n">
+        <v>2.4204545E7</v>
+      </c>
+      <c r="M69" s="13" t="n">
+        <v>2420455.0</v>
+      </c>
+      <c r="N69" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O69" s="13" t="n">
+        <v>2.6625E7</v>
+      </c>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q69" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K70" s="6"/>
+      <c r="L70" s="13" t="n">
+        <v>2.4444444E7</v>
+      </c>
+      <c r="M70" s="13" t="n">
+        <v>1955556.0</v>
+      </c>
+      <c r="N70" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O70" s="13" t="n">
+        <v>2.64E7</v>
+      </c>
+      <c r="P70" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q70" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>65.0</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K71" s="6"/>
+      <c r="L71" s="13" t="n">
+        <v>1.3609091E7</v>
+      </c>
+      <c r="M71" s="13" t="n">
+        <v>1360909.0</v>
+      </c>
+      <c r="N71" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O71" s="13" t="n">
+        <v>1.497E7</v>
+      </c>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q71" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>66.0</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K72" s="6"/>
+      <c r="L72" s="13" t="n">
+        <v>1.5272727E7</v>
+      </c>
+      <c r="M72" s="13" t="n">
+        <v>1527273.0</v>
+      </c>
+      <c r="N72" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O72" s="13" t="n">
+        <v>1.68E7</v>
+      </c>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>67.0</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K73" s="6"/>
+      <c r="L73" s="13" t="n">
+        <v>1600656.0</v>
+      </c>
+      <c r="M73" s="13" t="n">
+        <v>159344.0</v>
+      </c>
+      <c r="N73" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O73" s="13" t="n">
+        <v>1760000.0</v>
+      </c>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q73" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>68.0</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>2064</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K74" s="6"/>
+      <c r="L74" s="13" t="n">
+        <v>3.7363636E7</v>
+      </c>
+      <c r="M74" s="13" t="n">
+        <v>3736364.0</v>
+      </c>
+      <c r="N74" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O74" s="13" t="n">
+        <v>4.11E7</v>
+      </c>
+      <c r="P74" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q74" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>69.0</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>2089</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K75" s="6"/>
+      <c r="L75" s="13" t="n">
+        <v>3.2214141E7</v>
+      </c>
+      <c r="M75" s="13" t="n">
+        <v>3185859.0</v>
+      </c>
+      <c r="N75" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O75" s="13" t="n">
+        <v>3.54E7</v>
+      </c>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q75" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>C26MDH</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K76" s="6"/>
+      <c r="L76" s="13" t="n">
+        <v>1741667.0</v>
+      </c>
+      <c r="M76" s="13" t="n">
+        <v>139333.0</v>
+      </c>
+      <c r="N76" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O76" s="13" t="n">
+        <v>1881000.0</v>
+      </c>
+      <c r="P76" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>71.0</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>C26MDH</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K77" s="6"/>
+      <c r="L77" s="13" t="n">
+        <v>1429630.0</v>
+      </c>
+      <c r="M77" s="13" t="n">
+        <v>114370.0</v>
+      </c>
+      <c r="N77" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O77" s="13" t="n">
+        <v>1544000.0</v>
+      </c>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q77" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>72.0</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>C26MDH</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K78" s="6"/>
+      <c r="L78" s="13" t="n">
+        <v>1867591.0</v>
+      </c>
+      <c r="M78" s="13" t="n">
+        <v>149409.0</v>
+      </c>
+      <c r="N78" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O78" s="13" t="n">
+        <v>2017000.0</v>
+      </c>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q78" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>73.0</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>C26MYY</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>3502478885</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ LINH CHÂU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>Số 43 Đường Nguyễn Quyền, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K79" s="6"/>
+      <c r="L79" s="13" t="n">
+        <v>2036944.0</v>
+      </c>
+      <c r="M79" s="13" t="n">
+        <v>162956.0</v>
+      </c>
+      <c r="N79" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O79" s="13" t="n">
+        <v>2199900.0</v>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q79" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>74.0</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>C26MYY</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>1180</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>3502483525</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K80" s="6"/>
+      <c r="L80" s="13" t="n">
+        <v>2.5816345E7</v>
+      </c>
+      <c r="M80" s="13" t="n">
+        <v>2581635.0</v>
+      </c>
+      <c r="N80" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O80" s="13" t="n">
+        <v>2.839798E7</v>
+      </c>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q80" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>75.0</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>C26MYY</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>3502483525</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K81" s="6"/>
+      <c r="L81" s="13" t="n">
+        <v>3.6454545E7</v>
+      </c>
+      <c r="M81" s="13" t="n">
+        <v>3645455.0</v>
+      </c>
+      <c r="N81" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O81" s="13" t="n">
+        <v>4.01E7</v>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q81" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>76.0</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>C26MUN</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>6861</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>3502545972</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH UYÊN NGUYỄN</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>Số 03 đường Nguyễn Gia Thiều, Phường Phước Thắng, TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K82" s="6"/>
+      <c r="L82" s="13" t="n">
+        <v>1.054546E8</v>
+      </c>
+      <c r="M82" s="13" t="n">
+        <v>1.054546E7</v>
+      </c>
+      <c r="N82" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O82" s="13" t="n">
+        <v>1.1600006E8</v>
+      </c>
+      <c r="P82" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q82" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>77.0</v>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K83" s="6"/>
+      <c r="L83" s="13" t="n">
+        <v>1407408.0</v>
+      </c>
+      <c r="M83" s="13" t="n">
+        <v>112592.0</v>
+      </c>
+      <c r="N83" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O83" s="13" t="n">
+        <v>1520000.0</v>
+      </c>
+      <c r="P83" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q83" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>78.0</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K84" s="6"/>
+      <c r="L84" s="13" t="n">
+        <v>2.5555556E7</v>
+      </c>
+      <c r="M84" s="13" t="n">
+        <v>2044444.0</v>
+      </c>
+      <c r="N84" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O84" s="13" t="n">
+        <v>2.76E7</v>
+      </c>
+      <c r="P84" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q84" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>79.0</v>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K85" s="6"/>
+      <c r="L85" s="13" t="n">
+        <v>2592593.0</v>
+      </c>
+      <c r="M85" s="13" t="n">
+        <v>207407.0</v>
+      </c>
+      <c r="N85" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O85" s="13" t="n">
+        <v>2800000.0</v>
+      </c>
+      <c r="P85" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q85" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>80.0</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K86" s="6"/>
+      <c r="L86" s="13" t="n">
+        <v>4150000.0</v>
+      </c>
+      <c r="M86" s="13" t="n">
+        <v>332000.0</v>
+      </c>
+      <c r="N86" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O86" s="13" t="n">
+        <v>4482000.0</v>
+      </c>
+      <c r="P86" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q86" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>81.0</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K87" s="6"/>
+      <c r="L87" s="13" t="n">
         <v>1.6574074E7</v>
       </c>
-      <c r="M68" s="13" t="n">
+      <c r="M87" s="13" t="n">
         <v>1325926.0</v>
       </c>
-      <c r="N68" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O68" s="13" t="n">
+      <c r="N87" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O87" s="13" t="n">
         <v>1.79E7</v>
       </c>
-      <c r="P68" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q68" s="6" t="inlineStr">
+      <c r="P87" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q87" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>82.0</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I88" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K88" s="6"/>
+      <c r="L88" s="13" t="n">
+        <v>3.51852E7</v>
+      </c>
+      <c r="M88" s="13" t="n">
+        <v>2814816.0</v>
+      </c>
+      <c r="N88" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O88" s="13" t="n">
+        <v>3.8000016E7</v>
+      </c>
+      <c r="P88" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q88" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n">
+        <v>83.0</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K89" s="6"/>
+      <c r="L89" s="13" t="n">
+        <v>4672230.0</v>
+      </c>
+      <c r="M89" s="13" t="n">
+        <v>373778.0</v>
+      </c>
+      <c r="N89" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O89" s="13" t="n">
+        <v>5046008.0</v>
+      </c>
+      <c r="P89" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q89" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>
